--- a/Employee_Reports_wi48/Paul Jeric Azul Falcatan Q0478.xlsx
+++ b/Employee_Reports_wi48/Paul Jeric Azul Falcatan Q0478.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-131</v>
+        <v>-134</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-284</v>
+        <v>-287</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1093,11 +1093,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1191,11 +1191,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-86</v>
+        <v>-89</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1263,9 +1263,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>18-Apr-2025</t>
@@ -1277,11 +1289,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-86</v>
+        <v>-89</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1314,11 +1326,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1363,11 +1375,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1400,11 +1412,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1862,7 +1874,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>7650</v>
+        <v>7647</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -1891,7 +1903,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7838</v>
+        <v>7835</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
